--- a/MATH/M08/bus123-math-m08-l01-starter.xlsx
+++ b/MATH/M08/bus123-math-m08-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rff23cde8781d4481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R8903916bab9b4172"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R232d04b59e1942db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R80bc85de495946b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R4438c1992a184234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R9522befc8067471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rd4910f2964d84b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R6bcd7bbd5519440a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,15 +103,6 @@
     <x:t xml:space="preserve">What to model</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Input 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Input 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Input 3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Your formula / result</x:t>
   </x:si>
   <x:si>
@@ -193,40 +184,19 @@
     <x:t xml:space="preserve">Calculate simple future value</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Principal × (1 + rate × time).</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Optional Transfer · Manual PV vs Excel PV</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">C1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Manual simple-interest PV</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Future value divided by the simple discount factor.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">C2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Excel compound-periodic PV</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Use PV; keep Excel's cash-flow sign.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">C3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Round trip the Excel PV result with FV</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reference C2's negative PV result.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Self-check score</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Class Challenge · Discount, Reconcile, Recommend</x:t>
@@ -618,7 +588,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -663,6 +633,46 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4A7C5E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -730,7 +740,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -809,6 +819,51 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1143,7 +1198,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B17" s="6" t="str">
-        <x:v>Pause A (slide 9): G6:G10. Pause B (slide 11): G12:G14. Optional transfer (slide 17): G16:G18.</x:v>
+        <x:v>Checkpoint B (Canva 16–17): G12:G14. A (19–20): G6:G10. C (25–26): G16:G18. Record explanations at B31, B26, and B36.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
@@ -1233,8 +1288,8 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="20" t="s">
-        <x:v>25</x:v>
+      <x:c r="A1" s="20" t="str">
+        <x:v>Live You Try It · Checkpoints B → A → C</x:v>
       </x:c>
       <x:c r="B1" s="20" t="s">
         <x:v>25</x:v>
@@ -1262,8 +1317,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="21" t="s">
-        <x:v>26</x:v>
+      <x:c r="A2" s="21" t="str">
+        <x:v>Use current Canva page positions: B 16–17; A 19–20; C 25–26. Build the yellow cells, then explain below.</x:v>
       </x:c>
       <x:c r="B2" s="21" t="s">
         <x:v>26</x:v>
@@ -1292,7 +1347,7 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1"/>
     <x:row r="4" ht="30" customHeight="1"/>
-    <x:row r="5" ht="30" customHeight="1">
+    <x:row r="5" ht="68" customHeight="1">
       <x:c r="A5" s="7" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -1302,34 +1357,34 @@
       <x:c r="C5" s="7" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="s">
+      <x:c r="D5" s="31" t="str">
+        <x:v>Days / amount</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>Year basis / rate</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="str">
+        <x:v>Years / linked value</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="s">
+      <x:c r="H5" s="7" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="s">
+      <x:c r="I5" s="7" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="G5" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H5" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="I5" s="7" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="6" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="11">
         <x:v>75</x:v>
@@ -1344,18 +1399,18 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I6" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="6" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="14">
         <x:v>42000</x:v>
@@ -1372,18 +1427,18 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I7" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="6" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="11">
         <x:v>75</x:v>
@@ -1398,18 +1453,18 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I8" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="6" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="14">
         <x:v>42000</x:v>
@@ -1417,25 +1472,27 @@
       <x:c r="E9" s="15">
         <x:v>4.8000000000000001E-2</x:v>
       </x:c>
-      <x:c r="F9" s="30"/>
+      <x:c r="F9" s="45" t="str">
+        <x:f>IF(G8="","",G8)</x:f>
+      </x:c>
       <x:c r="G9" s="16"/>
       <x:c r="H9" s="10" t="str">
         <x:f>IF(G9="","Enter a formula using cell references",IF(ABS(G9-(D9*E9*F9))&lt;0.05,"Correct value - confirm formula bar uses references","Try again - reference the ordinary-time result"))</x:f>
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I9" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="6" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
         <x:f>IF(G7="","",G7)</x:f>
@@ -1450,47 +1507,47 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I10" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
-      <x:c r="A11" s="22" t="s">
-        <x:v>51</x:v>
+      <x:c r="A11" s="22" t="str">
+        <x:v>Checkpoint B · $18,500 loan · 6.2% annual simple interest · 8 months</x:v>
       </x:c>
       <x:c r="B11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="23" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I11" s="24" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B12" s="6" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="11">
         <x:v>8</x:v>
@@ -1505,18 +1562,18 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I12" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="6" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="14">
         <x:v>18500</x:v>
@@ -1533,75 +1590,73 @@
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
       <x:c r="I13" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="6" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D14" s="14">
         <x:v>18500</x:v>
       </x:c>
-      <x:c r="E14" s="15">
-        <x:v>6.2E-2</x:v>
-      </x:c>
-      <x:c r="F14" s="30" t="str">
-        <x:f>IF(G12="","",G12)</x:f>
-      </x:c>
+      <x:c r="E14" s="15" t="str">
+        <x:f>IF(G13="","",G13)</x:f>
+      </x:c>
+      <x:c r="F14" s="42"/>
       <x:c r="G14" s="16"/>
       <x:c r="H14" s="10" t="str">
-        <x:f>IF(G14="","Enter a formula using cell references",IF(ABS(G14-(D14*(1+E14*F14)))&lt;0.05,"Correct value - future value exceeds principal","Try again - include principal plus interest"))</x:f>
+        <x:f>IF(G14="","Enter a formula using cell references",IF(ABS(G14-(D14+E14))&lt;0.05,"Correct value - principal plus interest","Try again - include the original principal"))</x:f>
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
-      <x:c r="I14" s="13" t="s">
-        <x:v>60</x:v>
+      <x:c r="I14" s="13" t="str">
+        <x:v>Original principal plus the linked interest amount.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
-      <x:c r="A15" s="22" t="s">
-        <x:v>61</x:v>
+      <x:c r="A15" s="22" t="str">
+        <x:v>Checkpoint C · $30,000 future receipt · 6.5% annual compounding · 2 years</x:v>
       </x:c>
       <x:c r="B15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H15" s="23" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I15" s="24" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="6" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>Signed present outflow</x:v>
       </x:c>
       <x:c r="D16" s="14">
         <x:v>30000</x:v>
@@ -1609,83 +1664,181 @@
       <x:c r="E16" s="15">
         <x:v>6.5000000000000002E-2</x:v>
       </x:c>
-      <x:c r="F16" s="11">
-        <x:v>1.5</x:v>
+      <x:c r="F16" s="11" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G16" s="16"/>
       <x:c r="H16" s="10" t="str">
-        <x:f>IF(G16="","Enter a formula using cell references",IF(ABS(G16-(D16/(1+E16*F16)))&lt;0.05,"Correct simple-interest PV","Try again - divide by the simple discount factor"))</x:f>
+        <x:f>IF(G16="","Enter a formula using cell references",IF(ABS(G16-PV(E16,F16,0,D16))&lt;0.05,"Correct signed compound PV","Try again - check the rate, years, and sign"))</x:f>
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>64</x:v>
+      <x:c r="I16" s="13" t="str">
+        <x:v>Use PV with the positive future receipt.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="56" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B17" s="6" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C17" s="6" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D17" s="14">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="E17" s="15">
-        <x:v>6.5000000000000002E-2</x:v>
-      </x:c>
-      <x:c r="F17" s="11">
-        <x:v>1.5</x:v>
-      </x:c>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>Positive present-value magnitude</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:f>IF(G16="","",G16)</x:f>
+      </x:c>
+      <x:c r="E17" s="43"/>
+      <x:c r="F17" s="44"/>
       <x:c r="G17" s="16"/>
       <x:c r="H17" s="10" t="str">
-        <x:f>IF(G17="","Enter a formula using cell references",IF(ABS(G17-PV(E17,F17,0,D17))&lt;0.05,"Correct compound-periodic PV and sign","Try again - use PV with a positive future inflow"))</x:f>
+        <x:f>IF(G17="","Enter a formula using cell references",IF(ABS(G17-(-D17))&lt;0.05,"Correct positive PV magnitude","Try again - reverse the raw PV sign"))</x:f>
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
-      <x:c r="I17" s="13" t="s">
-        <x:v>67</x:v>
+      <x:c r="I17" s="13" t="str">
+        <x:v>Reverse the sign of the linked raw PV.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="56" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="6" t="n">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:f>IF(G17="","",G17)</x:f>
+        <x:f>IF(G16="","",G16)</x:f>
       </x:c>
       <x:c r="E18" s="15">
         <x:v>6.5000000000000002E-2</x:v>
       </x:c>
-      <x:c r="F18" s="11">
-        <x:v>1.5</x:v>
+      <x:c r="F18" s="11" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G18" s="16"/>
       <x:c r="H18" s="10" t="str">
-        <x:f>IF(G18="","Enter a formula using cell references",IF(ABS(G18-FV(E18,F18,0,D18))&lt;0.05,"Correct round trip","Try again - reference C2's PV result"))</x:f>
+        <x:f>IF(G18="","Enter a formula using cell references",IF(ABS(G18-FV(E18,F18,0,D18))&lt;0.05,"Correct round trip","Try again - use the signed PV result"))</x:f>
         <x:v>Enter a formula using cell references</x:v>
       </x:c>
-      <x:c r="I18" s="13" t="s">
-        <x:v>70</x:v>
+      <x:c r="I18" s="13" t="str">
+        <x:v>Use the signed PV linked in D18.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1"/>
     <x:row r="20" ht="70" customHeight="1">
-      <x:c r="A20" s="17" t="s">
-        <x:v>71</x:v>
+      <x:c r="A20" s="17" t="str">
+        <x:v>Progress</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
         <x:f>COUNTIF(H6:H18,"Correct*")&amp;" of 11 complete"</x:f>
         <x:v>0 of 11 complete</x:v>
       </x:c>
+    </x:row>
+    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="B25" s="46" t="str">
+        <x:v>A | Why does ordinary interest exceed exact interest?</x:v>
+      </x:c>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
+      <x:c r="G25" s="46"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="B26" s="47"/>
+      <x:c r="C26" s="47"/>
+      <x:c r="D26" s="47"/>
+      <x:c r="E26" s="47"/>
+      <x:c r="F26" s="47"/>
+      <x:c r="G26" s="47"/>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="B27" s="47"/>
+      <x:c r="C27" s="47"/>
+      <x:c r="D27" s="47"/>
+      <x:c r="E27" s="47"/>
+      <x:c r="F27" s="47"/>
+      <x:c r="G27" s="47"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="B28" s="47"/>
+      <x:c r="C28" s="47"/>
+      <x:c r="D28" s="47"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="47"/>
+      <x:c r="G28" s="47"/>
+    </x:row>
+    <x:row r="30" ht="34" customHeight="1">
+      <x:c r="B30" s="46" t="str">
+        <x:v>B | Distinguish principal, interest, and total repayment.</x:v>
+      </x:c>
+      <x:c r="C30" s="46"/>
+      <x:c r="D30" s="46"/>
+      <x:c r="E30" s="46"/>
+      <x:c r="F30" s="46"/>
+      <x:c r="G30" s="46"/>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="B31" s="47"/>
+      <x:c r="C31" s="47"/>
+      <x:c r="D31" s="47"/>
+      <x:c r="E31" s="47"/>
+      <x:c r="F31" s="47"/>
+      <x:c r="G31" s="47"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="B32" s="47"/>
+      <x:c r="C32" s="47"/>
+      <x:c r="D32" s="47"/>
+      <x:c r="E32" s="47"/>
+      <x:c r="F32" s="47"/>
+      <x:c r="G32" s="47"/>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="B33" s="47"/>
+      <x:c r="C33" s="47"/>
+      <x:c r="D33" s="47"/>
+      <x:c r="E33" s="47"/>
+      <x:c r="F33" s="47"/>
+      <x:c r="G33" s="47"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="B35" s="46" t="str">
+        <x:v>C | Explain the negative PV and the FV verification.</x:v>
+      </x:c>
+      <x:c r="C35" s="46"/>
+      <x:c r="D35" s="46"/>
+      <x:c r="E35" s="46"/>
+      <x:c r="F35" s="46"/>
+      <x:c r="G35" s="46"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="B36" s="47"/>
+      <x:c r="C36" s="47"/>
+      <x:c r="D36" s="47"/>
+      <x:c r="E36" s="47"/>
+      <x:c r="F36" s="47"/>
+      <x:c r="G36" s="47"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="B37" s="47"/>
+      <x:c r="C37" s="47"/>
+      <x:c r="D37" s="47"/>
+      <x:c r="E37" s="47"/>
+      <x:c r="F37" s="47"/>
+      <x:c r="G37" s="47"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="B38" s="47"/>
+      <x:c r="C38" s="47"/>
+      <x:c r="D38" s="47"/>
+      <x:c r="E38" s="47"/>
+      <x:c r="F38" s="47"/>
+      <x:c r="G38" s="47"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1693,6 +1846,12 @@
     <x:mergeCell ref="A2:I2"/>
     <x:mergeCell ref="A11:I11"/>
     <x:mergeCell ref="A15:I15"/>
+    <x:mergeCell ref="B25:G25"/>
+    <x:mergeCell ref="B26:G28"/>
+    <x:mergeCell ref="B30:G30"/>
+    <x:mergeCell ref="B31:G33"/>
+    <x:mergeCell ref="B35:G35"/>
+    <x:mergeCell ref="B36:G38"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="H6:H18">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Correct"/>
@@ -1720,118 +1879,118 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H1" s="20" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H2" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1"/>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="22" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G4" s="23" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H4" s="24" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H5" s="7" t="s">
-        <x:v>82</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48">
       <x:c r="A6" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D6" s="14">
         <x:v>-27306.68</x:v>
@@ -1847,92 +2006,92 @@
         <x:v>2.25</x:v>
       </x:c>
       <x:c r="H6" s="13" t="s">
-        <x:v>86</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1"/>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="22" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G8" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H8" s="24" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B9" s="14">
         <x:v>75000</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D9" s="15">
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="E9" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G9" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1"/>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E11" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F11" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>82</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="6">
         <x:v>1</x:v>
@@ -1946,18 +2105,18 @@
       </x:c>
       <x:c r="E12" s="16"/>
       <x:c r="F12" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G12" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H12" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B13" s="6">
         <x:v>2</x:v>
@@ -1971,18 +2130,18 @@
       </x:c>
       <x:c r="E13" s="16"/>
       <x:c r="F13" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G13" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H13" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B14" s="6">
         <x:v>3</x:v>
@@ -1996,18 +2155,18 @@
       </x:c>
       <x:c r="E14" s="16"/>
       <x:c r="F14" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G14" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H14" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B15" s="6">
         <x:v>4</x:v>
@@ -2021,18 +2180,18 @@
       </x:c>
       <x:c r="E15" s="16"/>
       <x:c r="F15" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G15" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H15" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B16" s="6">
         <x:v>5</x:v>
@@ -2046,179 +2205,179 @@
       </x:c>
       <x:c r="E16" s="16"/>
       <x:c r="F16" s="13" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H16" s="13" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B17" s="6"/>
       <x:c r="C17" s="6"/>
       <x:c r="D17" s="6"/>
       <x:c r="E17" s="16"/>
       <x:c r="F17" s="13" t="s">
-        <x:v>107</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G17" s="13" t="s">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H17" s="13" t="s">
-        <x:v>109</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B18" s="6"/>
       <x:c r="C18" s="6"/>
       <x:c r="D18" s="6"/>
       <x:c r="E18" s="16"/>
       <x:c r="F18" s="13" t="s">
-        <x:v>111</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G18" s="13" t="s">
-        <x:v>112</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H18" s="13" t="s">
-        <x:v>113</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B19" s="26" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C19" s="26" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D19" s="26" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E19" s="26" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F19" s="27" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G19" s="27" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H19" s="27" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="25" t="s">
-        <x:v>117</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B20" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C20" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D20" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E20" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F20" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G20" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H20" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="25" t="s">
-        <x:v>117</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B21" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C21" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D21" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E21" s="26" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F21" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G21" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H21" s="27" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="25" t="s">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B22" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D22" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E22" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F22" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G22" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H22" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
       <x:c r="A23" s="25" t="s">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B23" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D23" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E23" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F23" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G23" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H23" s="27" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2257,200 +2416,200 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B1" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C1" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D1" s="28" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B2" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C2" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D2" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1"/>
     <x:row r="4" ht="34" customHeight="1"/>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="52" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="52" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="52" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="52" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="52" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="52" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>158</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="52" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>162</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="52" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>170</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
